--- a/Result/profitability/3533.xlsx
+++ b/Result/profitability/3533.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>17.0275</v>
+        <v>16.94625</v>
       </c>
       <c r="N2" t="n">
-        <v>48.12625</v>
+        <v>47.2325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>14.8425</v>
+        <v>13.80875</v>
       </c>
       <c r="N3" t="n">
-        <v>44.64875</v>
+        <v>43.68875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>11.81875</v>
+        <v>11.50125</v>
       </c>
       <c r="N4" t="n">
-        <v>41.64</v>
+        <v>40.89</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>9.348750000000001</v>
+        <v>10.7225</v>
       </c>
       <c r="N5" t="n">
-        <v>38.095</v>
+        <v>37.40375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>8.55625</v>
+        <v>8.1775</v>
       </c>
       <c r="N6" t="n">
-        <v>34.20625</v>
+        <v>33.48875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>6.0925</v>
+        <v>5.48875</v>
       </c>
       <c r="N7" t="n">
-        <v>31.4775</v>
+        <v>30.71875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>2.94</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64625</v>
+        <v>3.185</v>
       </c>
       <c r="N8" t="n">
-        <v>29.52625</v>
+        <v>29.01625</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9569</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5218</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4351</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>495</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2598</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1984</v>
+      </c>
+      <c r="L75" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="M75" t="n">
+        <v>19.1825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.75125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-3.690000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1726719700514741</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.079999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08234106962663967</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.642750373692078</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.530000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1084313725490196</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
